--- a/table/Supplementary Table 17.xlsx
+++ b/table/Supplementary Table 17.xlsx
@@ -7,8 +7,10 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="A - Drift basis" sheetId="1" r:id="rId1"/>
-    <sheet name="B - Impact in 2050" sheetId="2" r:id="rId2"/>
+    <sheet name="A - Specification" sheetId="1" r:id="rId1"/>
+    <sheet name="B - Residual correlation" sheetId="2" r:id="rId2"/>
+    <sheet name="C - Eigenvalues" sheetId="3" r:id="rId3"/>
+    <sheet name="D - Non-negativity" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -344,119 +346,187 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Income group</t>
+          <t>Element</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Effective VSLY in 1990</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Effective VSLY in 2023</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Endpoint CAGR (%/year, published basis)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Log-linear OLS CAGR (%/year, bounding check)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Log-linear R squared</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Difference (percentage points per year)</t>
+          <t>Specification</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Low income</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>13513.84832241552</v>
-      </c>
-      <c r="C2">
-        <v>13652.93797022442</v>
-      </c>
-      <c r="D2">
-        <v>0.03103443000165296</v>
-      </c>
-      <c r="E2">
-        <v>0.01957712549367496</v>
-      </c>
-      <c r="F2">
-        <v>0.1316077380194902</v>
-      </c>
-      <c r="G2">
-        <v>-0.01145730450797799</v>
+          <t>Estimand</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Income-group DALYs; VLW obtained by monetising DALY draws</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lower middle income</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>57351.02733142021</v>
-      </c>
-      <c r="C3">
-        <v>60365.1625571617</v>
-      </c>
-      <c r="D3">
-        <v>0.1553368954030798</v>
-      </c>
-      <c r="E3">
-        <v>0.1715897613505657</v>
-      </c>
-      <c r="F3">
-        <v>0.7870660069175858</v>
-      </c>
-      <c r="G3">
-        <v>0.01625286594748587</v>
+          <t>Group models</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Three income-group series fitted independently with ARIMA</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Upper middle income</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>142924.1507636413</v>
-      </c>
-      <c r="C4">
-        <v>140261.0422245954</v>
-      </c>
-      <c r="D4">
-        <v>-0.05698012851151901</v>
-      </c>
-      <c r="E4">
-        <v>-0.07747190461725451</v>
-      </c>
-      <c r="F4">
-        <v>0.8224230630783551</v>
-      </c>
-      <c r="G4">
-        <v>-0.02049177610573549</v>
+          <t>Coupling</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Draws summed across the three income groups at each horizon</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Correlation type</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cross-sectional Pearson correlation of in-sample model residuals between groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Correlation estimation</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Estimated once on the full 1990-2023 fit, use='pairwise.complete.obs'; held fixed across horizons</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Positive-definite adjustment</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Eigenvalue clipping at 1e-08 after symmetrisation, then cov2cor rescaling; not Higham's algorithm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Parameter treatment</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fixed at point estimates; parameter-estimation and model uncertainty are NOT propagated</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Marginal dispersion</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Backed out of the marginal forecast interval as (upper - lower) / (2 * z_0.975)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Draws per horizon</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Seed rule</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>set.seed(20260725 + k) at horizon k; independent stream per horizon</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Non-negativity</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>No truncation applied; the number of non-positive draws is counted and reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Temporal structure</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Horizons simulated independently; draws are pointwise per year and are NOT temporal paths</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Interval interpretation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Model-dependent scenario range; the nominal 95% level is a construction parameter only</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Valuation</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Fixed 2023 group-specific effective VSLY</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -466,61 +536,962 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>Matrix</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Fixed-composition VLW in 2050 (billion constant-2023 USD)</t>
+          <t>Income group</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Drift-adjusted VLW in 2050 (billion constant-2023 USD)</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Difference (%)</t>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Endpoint CAGR, 1990 and 2023 only (published basis)</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>1195.059287771596</v>
+          <t>Raw Pearson</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
       </c>
       <c r="C2">
-        <v>1189.195770368219</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>-0.4906465698711338</v>
+        <v>0.4820699626081297</v>
+      </c>
+      <c r="E2">
+        <v>0.7015810517986524</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Log-linear OLS on all 34 annual observations (bounding check)</t>
-        </is>
+          <t>Raw Pearson</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>0.4820699626081297</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0.6455903471929817</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Raw Pearson</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0.7015810517986524</v>
+      </c>
+      <c r="D4">
+        <v>0.6455903471929817</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>After eigenvalue clipping</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>0.4820699626081305</v>
+      </c>
+      <c r="E5">
+        <v>0.7015810517986526</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>After eigenvalue clipping</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>0.4820699626081305</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>0.6455903471929818</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>After eigenvalue clipping</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>0.7015810517986525</v>
+      </c>
+      <c r="D7">
+        <v>0.6455903471929818</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Eigenvalue before adjustment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Eigenvalue after clipping</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Clip was binding</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2.223997295035499</v>
+      </c>
+      <c r="C2">
+        <v>2.223997295035499</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>1195.059287771596</v>
+        <v>0.5212953275523868</v>
       </c>
       <c r="C3">
-        <v>1184.824913221494</v>
+        <v>0.5212953275523868</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>0.2547073774121137</v>
+      </c>
+      <c r="C4">
+        <v>0.2547073774121137</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Draws per horizon</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Non-positive group draws</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Non-positive group draws (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Non-positive aggregate draws</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Non-positive aggregate draws (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>2024</v>
+      </c>
+      <c r="C2">
+        <v>50000</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>2025</v>
+      </c>
+      <c r="C3">
+        <v>50000</v>
       </c>
       <c r="D3">
-        <v>-0.8563905284720952</v>
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>2026</v>
+      </c>
+      <c r="C4">
+        <v>50000</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>2027</v>
+      </c>
+      <c r="C5">
+        <v>50000</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2028</v>
+      </c>
+      <c r="C6">
+        <v>50000</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>2029</v>
+      </c>
+      <c r="C7">
+        <v>50000</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>2030</v>
+      </c>
+      <c r="C8">
+        <v>50000</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>2031</v>
+      </c>
+      <c r="C9">
+        <v>50000</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>2032</v>
+      </c>
+      <c r="C10">
+        <v>50000</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2033</v>
+      </c>
+      <c r="C11">
+        <v>50000</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>2034</v>
+      </c>
+      <c r="C12">
+        <v>50000</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>2035</v>
+      </c>
+      <c r="C13">
+        <v>50000</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>2036</v>
+      </c>
+      <c r="C14">
+        <v>50000</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>2037</v>
+      </c>
+      <c r="C15">
+        <v>50000</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>2038</v>
+      </c>
+      <c r="C16">
+        <v>50000</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>2039</v>
+      </c>
+      <c r="C17">
+        <v>50000</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>2040</v>
+      </c>
+      <c r="C18">
+        <v>50000</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>2041</v>
+      </c>
+      <c r="C19">
+        <v>50000</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>2042</v>
+      </c>
+      <c r="C20">
+        <v>50000</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>2043</v>
+      </c>
+      <c r="C21">
+        <v>50000</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>2044</v>
+      </c>
+      <c r="C22">
+        <v>50000</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>2045</v>
+      </c>
+      <c r="C23">
+        <v>50000</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>2046</v>
+      </c>
+      <c r="C24">
+        <v>50000</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>2047</v>
+      </c>
+      <c r="C25">
+        <v>50000</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>2048</v>
+      </c>
+      <c r="C26">
+        <v>50000</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>2049</v>
+      </c>
+      <c r="C27">
+        <v>50000</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>2050</v>
+      </c>
+      <c r="C28">
+        <v>50000</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
